--- a/artfynd/A 64562-2023 artfynd.xlsx
+++ b/artfynd/A 64562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122767242</v>
       </c>
       <c r="B2" t="n">
-        <v>97301</v>
+        <v>97309</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64562-2023 artfynd.xlsx
+++ b/artfynd/A 64562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122767242</v>
       </c>
       <c r="B2" t="n">
-        <v>97309</v>
+        <v>97311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64562-2023 artfynd.xlsx
+++ b/artfynd/A 64562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122767242</v>
       </c>
       <c r="B2" t="n">
-        <v>97311</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64562-2023 artfynd.xlsx
+++ b/artfynd/A 64562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122767242</v>
       </c>
       <c r="B2" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64562-2023 artfynd.xlsx
+++ b/artfynd/A 64562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122767242</v>
       </c>
       <c r="B2" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 64562-2023 artfynd.xlsx
+++ b/artfynd/A 64562-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122767242</v>
       </c>
       <c r="B2" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
